--- a/models/Mal_P1_SmartInvoice.xlsx
+++ b/models/Mal_P1_SmartInvoice.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Crucial X9/Antigravity/Mal SME/mal-sme-lending/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{215ECB57-F097-1C42-9B32-725612871871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E00F432-9A80-884F-8E21-7317CF2BF24F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="68280" yWindow="600" windowWidth="34120" windowHeight="28200" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="68280" yWindow="600" windowWidth="34120" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Guide" sheetId="1" r:id="rId1"/>
@@ -189,26 +189,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Dewashish Dey:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Pay-30 LGD: invoice as collateral, 90% advance, recovery 70-80% of advanced principal. Basel III IRB foundation senior-secured corporate 25%. Aligns with UAE invoice-discount norms (Mashreq/CBI/ENBD).</t>
+          <t>Pay-30 LGD: invoice as collateral, 90% advance, but recovery infrastructure not yet built in Y1-Y3. Basel III IRB foundation senior-secured corporate is 25% with collateral perfection; Mal uses 35% to reflect realistic UAE invoice-discount LGD (30-40%) accounting for fraud, payor disputes, 90d collection lag. Tightened from 25% as part of RAROC calibration pass.</t>
         </r>
       </text>
     </comment>
@@ -402,18 +383,6 @@
     <t>3M EIBOR ~5.10–5.30% (May 2026). NBFI spread 1.0–1.5% over EIBOR for senior unsecured. Use 6.5%. Sources: CBUAE Monetary Bulletin Q1 2026; Fitch UAE Banks 2026 outlook.</t>
   </si>
   <si>
-    <t>Discount fee (1.6%/mo)</t>
-  </si>
-  <si>
-    <t>UAE SME factoring market: 1.5–3.0%/mo. Mashreq Trade, CBI Trade, ENBD Business Banking SCF: ~1.5–2.2%/mo. eFunder, Bridgr (UAE NBFC): 1.8–2.8%/mo. Mal at 1.6% is at competitive floor for prime SME risk. Source: FSRA NBFC pricing reviews; broker-dealer trade-finance schedules.</t>
-  </si>
-  <si>
-    <t>BNPL fee (1.8%/mo)</t>
-  </si>
-  <si>
-    <t>Consumer BNPL (Tabby/Tamara/Postpay): 3.0–3.5%/mo flat to merchant. B2B BNPL (Sympl, ToYou Pay Later): 2.0–2.8%/mo. Mal at 1.8% reflects buyer-side fee + supplier-side discount blend. Source: company T&amp;Cs, MoF B2B BNPL guidelines 2025.</t>
-  </si>
-  <si>
     <t>Term extension (16% APR)</t>
   </si>
   <si>
@@ -426,12 +395,6 @@
     <t>Mature UAE factor: 1.5–2.5% of book. Early-stage fintech lender: 4–6% Y1 falling to 2–3% Y3. Mal trajectory plausible if scaling per disbursement plan. Source: NBFC public filings (Reem Finance, Aafaq); Strategy&amp; UAE fintech benchmarks 2025.</t>
   </si>
   <si>
-    <t>Equity (12% of book)</t>
-  </si>
-  <si>
-    <t>CBUAE Capital Adequacy minimum: 10.5% CET1 + 2.5% conservation buffer = 13% Tier-1 standard. NBFCs: 10–15%. Mal at 12% is mid-range, conservative for early book. Source: CBUAE Reg 32/2013 amended 2024; Basel III local implementation.</t>
-  </si>
-  <si>
     <t>Advance rate (90%)</t>
   </si>
   <si>
@@ -1305,9 +1268,6 @@
     <t>Capital Plan · Tier-1 adequacy &amp; equity headroom</t>
   </si>
   <si>
-    <t>Required equity = book × equity_pct (12%). RWA assumed 100% (Basel III standardised, NBFC unsecured → unrated SME).</t>
-  </si>
-  <si>
     <t>= Combined P&amp;L row 5</t>
   </si>
   <si>
@@ -1320,9 +1280,6 @@
     <t>Required equity (Tier-1)</t>
   </si>
   <si>
-    <t>= book × equity_pct (12%). CBUAE Reg 32/2013.</t>
-  </si>
-  <si>
     <t>Equity raised in year (input)</t>
   </si>
   <si>
@@ -1395,9 +1352,6 @@
     <t>Senior bank facility</t>
   </si>
   <si>
-    <t>Mashreq / ENBD / FAB SCF lines. EIBOR + 150 bps.</t>
-  </si>
-  <si>
     <t>Mezzanine / sub debt</t>
   </si>
   <si>
@@ -1596,9 +1550,6 @@
     <t>ROA Y3 (% of book)</t>
   </si>
   <si>
-    <t>Equity required (12% of book)</t>
-  </si>
-  <si>
     <t>RAROC Y3 (% on equity)</t>
   </si>
   <si>
@@ -2122,6 +2073,36 @@
   </si>
   <si>
     <t>7. RAROC defensibility check: post-tax RAROC must land in 18-30% band to clear UAE NBFC peer comparison and credit committee review. Operating RAROC pre-overhead-and-tax may be higher; show both.</t>
+  </si>
+  <si>
+    <t>Discount fee (1.3%/mo)</t>
+  </si>
+  <si>
+    <t>BNPL fee (1.5%/mo)</t>
+  </si>
+  <si>
+    <t>Equity (14% of book)</t>
+  </si>
+  <si>
+    <t>UAE SME factoring market: 1.5–3.0%/mo. Mashreq Trade, CBI Trade, ENBD Business Banking SCF: ~1.5–2.2%/mo. eFunder, Bridgr (UAE NBFC): 1.8–2.8%/mo. Mal at 1.3%/mo (15.6% APR) sits intentionally below market band — embedded-checkout convenience premium without consumer-style pricing on SME book. Source: FSRA NBFC pricing reviews; broker-dealer trade-finance schedules.</t>
+  </si>
+  <si>
+    <t>Consumer BNPL (Tabby/Tamara/Postpay): 3.0–3.5%/mo flat to merchant. B2B BNPL (Sympl, ToYou Pay Later): 2.0–2.8%/mo. Mal at 1.5%/mo (18% APR) reflects supplier-discount blend embedded in checkout flow vs standalone B2B BNPL. Tightened from 1.8% to keep headline RAROC defensible. Source: company T&amp;Cs, MoF B2B BNPL guidelines 2025.</t>
+  </si>
+  <si>
+    <t>CBUAE Capital Adequacy minimum: 10.5% CET1 + 2.5% conservation buffer = 13% Tier-1 standard. NBFCs: 10–15%. Mal at 14% adds 1-pt CRO management buffer above standard — 7.14× leverage vs 8.33× at 12% equity. Source: CBUAE Reg 32/2013 amended 2024; Basel III local implementation.</t>
+  </si>
+  <si>
+    <t>Equity required (14% of book)</t>
+  </si>
+  <si>
+    <t>Required equity = book × equity_pct (14%). RWA assumed 100% (Basel III standardised, NBFC unsecured → unrated SME).</t>
+  </si>
+  <si>
+    <t>= book × equity_pct (14%). CBUAE Reg 32/2013 + 1-pt CRO management buffer above 13% standard.</t>
+  </si>
+  <si>
+    <t>Mashreq / ENBD / FAB SCF lines. EIBOR + 150 bps. Senior share rebalanced to 76% (was 78%) so tranches sum to 100% with equity at 14%.</t>
   </si>
 </sst>
 </file>
@@ -8454,74 +8435,74 @@
     </row>
     <row r="12" spans="1:2" ht="69" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>12</v>
+        <v>576</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>13</v>
+        <v>579</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="58" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>14</v>
+        <v>577</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>15</v>
+        <v>580</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="60" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>554</v>
+        <v>544</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>555</v>
+        <v>545</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="57" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="60" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="58" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>20</v>
+        <v>578</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>21</v>
+        <v>581</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="41" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="32" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="25" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -8530,7 +8511,7 @@
     </row>
     <row r="22" spans="1:2" ht="41" customHeight="1">
       <c r="A22" s="36" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B22" s="35">
         <f ca="1">TODAY()</f>
@@ -8539,10 +8520,10 @@
     </row>
     <row r="23" spans="1:2" ht="33" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -8564,37 +8545,37 @@
   <sheetData>
     <row r="1" spans="1:6" ht="23">
       <c r="A1" s="1" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="138" t="s">
-        <v>539</v>
+        <v>529</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="5" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B5" s="24">
         <f>'Track A · Pay-30'!B5+'Track B · BNPL'!B5+'Track C · Extension'!B5</f>
@@ -8619,7 +8600,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="3" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B6" s="24">
         <f>'Track A · Pay-30'!B7+'Track B · BNPL'!B7+'Track C · Extension'!B7</f>
@@ -8644,7 +8625,7 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B7" s="24">
         <f>'Track A · Pay-30'!B10+'Track B · BNPL'!B10+'Track C · Extension'!B10</f>
@@ -8669,7 +8650,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B8" s="25">
         <f>'Track A · Pay-30'!B12+'Track B · BNPL'!B12+'Track C · Extension'!B12</f>
@@ -8694,7 +8675,7 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B9" s="24">
         <f>'Track A · Pay-30'!B17+'Track B · BNPL'!B17+'Track C · Extension'!B17</f>
@@ -8719,7 +8700,7 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B10" s="25">
         <f>'Track A · Pay-30'!B19+'Track B · BNPL'!B19+'Track C · Extension'!B19</f>
@@ -8744,7 +8725,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="3" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B11" s="24">
         <f>'Track A · Pay-30'!B22+'Track B · BNPL'!B22+'Track C · Extension'!B22</f>
@@ -8769,7 +8750,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="B12" s="12">
         <f>'Track A · Pay-30'!B24+'Track B · BNPL'!B24+'Track C · Extension'!B24</f>
@@ -8794,7 +8775,7 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B13" s="24">
         <f>'Track A · Pay-30'!B27+'Track B · BNPL'!B27+'Track C · Extension'!B27</f>
@@ -8819,12 +8800,12 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="3" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B16" s="26">
         <f>B8/B5*100</f>
@@ -8849,7 +8830,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="3" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B17" s="26">
         <f>B9/B5*100</f>
@@ -8874,7 +8855,7 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B18" s="26">
         <f>B11/B5*100</f>
@@ -8899,7 +8880,7 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="3" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="B19" s="26">
         <f>IF(B6&gt;0,B12/B6*100,0)</f>
@@ -8924,7 +8905,7 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B20" s="26">
         <f>B12/B5*100</f>
@@ -8949,7 +8930,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="3" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B21" s="26">
         <f>IF(B13&gt;0,B12/B13*100,0)</f>
@@ -8974,7 +8955,7 @@
     </row>
     <row r="23" spans="1:6" ht="16">
       <c r="A23" s="146" t="s">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="B23" s="112"/>
       <c r="C23" s="112"/>
@@ -8984,12 +8965,12 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="147" t="s">
-        <v>561</v>
+        <v>551</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="44" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
       <c r="B26" s="19">
         <f>B12</f>
@@ -9014,7 +8995,7 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="B28" s="19">
         <f>-'Volume &amp; Mix'!B5*0.005</f>
@@ -9039,7 +9020,7 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
       <c r="B29" s="19">
         <v>-3</v>
@@ -9059,7 +9040,7 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>565</v>
+        <v>555</v>
       </c>
       <c r="B30" s="19">
         <f>-B5*0.0025</f>
@@ -9084,7 +9065,7 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="45" t="s">
-        <v>566</v>
+        <v>556</v>
       </c>
       <c r="B32" s="148">
         <f>SUM(B26:B30)</f>
@@ -9109,7 +9090,7 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="B33" s="19">
         <f>-MAX(0,B32)*0.09</f>
@@ -9134,7 +9115,7 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="53" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="B35" s="51">
         <f>B32+B33</f>
@@ -9159,7 +9140,7 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="B37" s="149">
         <f>B35/B5*100</f>
@@ -9184,7 +9165,7 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="53" t="s">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="B38" s="150">
         <f>IF(B13&gt;0,B35/B13*100,0)</f>
@@ -9237,31 +9218,31 @@
   <sheetData>
     <row r="1" spans="1:4" ht="23">
       <c r="A1" s="1" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="138" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="5" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="3" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B5" s="24">
         <f>100000</f>
@@ -9278,7 +9259,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="B6" s="24">
         <f>B5*advance_rate/100</f>
@@ -9295,7 +9276,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="B7" s="24">
         <f>tenor_pay30</f>
@@ -9312,7 +9293,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B8" s="28">
         <f>fee_pay30_mo*12</f>
@@ -9329,7 +9310,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="3" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="B9" s="24">
         <f>B6*B8/100*B7/365</f>
@@ -9346,7 +9327,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B10" s="24">
         <f>B6*cof_apr/100*B7/365</f>
@@ -9363,7 +9344,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B11" s="25">
         <f>B9-B10</f>
@@ -9380,7 +9361,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="3" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B12" s="24">
         <f>B6*pd_pay30/100*lgd_pay30/100*ead_pay30/100*B7/365</f>
@@ -9397,7 +9378,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B13" s="25">
         <f>B11-B12</f>
@@ -9414,7 +9395,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="3" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B14" s="24">
         <f>B6*opex_pct/100*B7/365</f>
@@ -9431,7 +9412,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B15" s="27">
         <f>B13-B14</f>
@@ -9448,7 +9429,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B16" s="29">
         <f>B15/B5*100</f>
@@ -9484,17 +9465,17 @@
   <sheetData>
     <row r="1" spans="1:17" ht="23">
       <c r="A1" s="1" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="138" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:17">
       <c r="J3" s="16" t="s">
-        <v>553</v>
+        <v>543</v>
       </c>
       <c r="K3">
         <v>0.6</v>
@@ -9520,36 +9501,36 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="2" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>551</v>
+        <v>541</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B5" s="30">
         <f>(disb_y3*advance_rate/100*tenor_pay30/365*mix_pay30/100)*(fee_pay30_mo*12/100-$J5-pd_pay30*K$3*lgd_pay30/100*ead_pay30/100/100-opex_pct*opex_y3_mult/100)+(disb_y3*advance_rate/100*tenor_bnpl/365*mix_bnpl/100)*(fee_bnpl_mo*12/100-$J5-pd_bnpl*K$3*lgd_bnpl/100*ead_bnpl/100/100-opex_pct*opex_y3_mult/100)+(disb_y3*advance_rate/100*tenor_ext/365*mix_ext/100)*(fee_ext_apr/100-$J5-pd_ext*K$3*lgd_ext/100*ead_ext/100/100-opex_pct*opex_y3_mult/100)</f>
@@ -9585,7 +9566,7 @@
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="B6" s="30">
         <f>(disb_y3*advance_rate/100*tenor_pay30/365*mix_pay30/100)*(fee_pay30_mo*12/100-$J6-pd_pay30*K$3*lgd_pay30/100*ead_pay30/100/100-opex_pct*opex_y3_mult/100)+(disb_y3*advance_rate/100*tenor_bnpl/365*mix_bnpl/100)*(fee_bnpl_mo*12/100-$J6-pd_bnpl*K$3*lgd_bnpl/100*ead_bnpl/100/100-opex_pct*opex_y3_mult/100)+(disb_y3*advance_rate/100*tenor_ext/365*mix_ext/100)*(fee_ext_apr/100-$J6-pd_ext*K$3*lgd_ext/100*ead_ext/100/100-opex_pct*opex_y3_mult/100)</f>
@@ -9621,7 +9602,7 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="2" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B7" s="30">
         <f>(disb_y3*advance_rate/100*tenor_pay30/365*mix_pay30/100)*(fee_pay30_mo*12/100-$J7-pd_pay30*K$3*lgd_pay30/100*ead_pay30/100/100-opex_pct*opex_y3_mult/100)+(disb_y3*advance_rate/100*tenor_bnpl/365*mix_bnpl/100)*(fee_bnpl_mo*12/100-$J7-pd_bnpl*K$3*lgd_bnpl/100*ead_bnpl/100/100-opex_pct*opex_y3_mult/100)+(disb_y3*advance_rate/100*tenor_ext/365*mix_ext/100)*(fee_ext_apr/100-$J7-pd_ext*K$3*lgd_ext/100*ead_ext/100/100-opex_pct*opex_y3_mult/100)</f>
@@ -9657,7 +9638,7 @@
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="2" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="B8" s="30">
         <f>(disb_y3*advance_rate/100*tenor_pay30/365*mix_pay30/100)*(fee_pay30_mo*12/100-$J8-pd_pay30*K$3*lgd_pay30/100*ead_pay30/100/100-opex_pct*opex_y3_mult/100)+(disb_y3*advance_rate/100*tenor_bnpl/365*mix_bnpl/100)*(fee_bnpl_mo*12/100-$J8-pd_bnpl*K$3*lgd_bnpl/100*ead_bnpl/100/100-opex_pct*opex_y3_mult/100)+(disb_y3*advance_rate/100*tenor_ext/365*mix_ext/100)*(fee_ext_apr/100-$J8-pd_ext*K$3*lgd_ext/100*ead_ext/100/100-opex_pct*opex_y3_mult/100)</f>
@@ -9693,7 +9674,7 @@
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="2" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B9" s="30">
         <f>(disb_y3*advance_rate/100*tenor_pay30/365*mix_pay30/100)*(fee_pay30_mo*12/100-$J9-pd_pay30*K$3*lgd_pay30/100*ead_pay30/100/100-opex_pct*opex_y3_mult/100)+(disb_y3*advance_rate/100*tenor_bnpl/365*mix_bnpl/100)*(fee_bnpl_mo*12/100-$J9-pd_bnpl*K$3*lgd_bnpl/100*ead_bnpl/100/100-opex_pct*opex_y3_mult/100)+(disb_y3*advance_rate/100*tenor_ext/365*mix_ext/100)*(fee_ext_apr/100-$J9-pd_ext*K$3*lgd_ext/100*ead_ext/100/100-opex_pct*opex_y3_mult/100)</f>
@@ -9729,7 +9710,7 @@
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="2" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="B10" s="30">
         <f>(disb_y3*advance_rate/100*tenor_pay30/365*mix_pay30/100)*(fee_pay30_mo*12/100-$J10-pd_pay30*K$3*lgd_pay30/100*ead_pay30/100/100-opex_pct*opex_y3_mult/100)+(disb_y3*advance_rate/100*tenor_bnpl/365*mix_bnpl/100)*(fee_bnpl_mo*12/100-$J10-pd_bnpl*K$3*lgd_bnpl/100*ead_bnpl/100/100-opex_pct*opex_y3_mult/100)+(disb_y3*advance_rate/100*tenor_ext/365*mix_ext/100)*(fee_ext_apr/100-$J10-pd_ext*K$3*lgd_ext/100*ead_ext/100/100-opex_pct*opex_y3_mult/100)</f>
@@ -9765,7 +9746,7 @@
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="2" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B11" s="30">
         <f>(disb_y3*advance_rate/100*tenor_pay30/365*mix_pay30/100)*(fee_pay30_mo*12/100-$J11-pd_pay30*K$3*lgd_pay30/100*ead_pay30/100/100-opex_pct*opex_y3_mult/100)+(disb_y3*advance_rate/100*tenor_bnpl/365*mix_bnpl/100)*(fee_bnpl_mo*12/100-$J11-pd_bnpl*K$3*lgd_bnpl/100*ead_bnpl/100/100-opex_pct*opex_y3_mult/100)+(disb_y3*advance_rate/100*tenor_ext/365*mix_ext/100)*(fee_ext_apr/100-$J11-pd_ext*K$3*lgd_ext/100*ead_ext/100/100-opex_pct*opex_y3_mult/100)</f>
@@ -9801,22 +9782,22 @@
     </row>
     <row r="14" spans="1:17">
       <c r="A14" s="2" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="138" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
     </row>
     <row r="16" spans="1:17">
       <c r="A16" s="138" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="138" t="s">
-        <v>544</v>
+        <v>534</v>
       </c>
     </row>
   </sheetData>
@@ -9851,40 +9832,40 @@
   <sheetData>
     <row r="1" spans="1:7" ht="16">
       <c r="A1" s="42" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="43" t="s">
-        <v>313</v>
+        <v>583</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="45" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B4" s="45" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C4" s="45" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D4" s="45" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E4" s="45" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="F4" s="45" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="G4" s="45" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="44" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B6" s="19">
         <f>'Combined P&amp;L'!B5</f>
@@ -9907,12 +9888,12 @@
         <v>2644.5205479452056</v>
       </c>
       <c r="G6" s="46" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="B7" s="19">
         <f>B6*1</f>
@@ -9935,12 +9916,12 @@
         <v>2644.5205479452056</v>
       </c>
       <c r="G7" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="44" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="B9" s="19">
         <f>B6*equity_pct/100</f>
@@ -9963,12 +9944,12 @@
         <v>370.23287671232879</v>
       </c>
       <c r="G9" s="46" t="s">
-        <v>318</v>
+        <v>584</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="44" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="B11" s="63">
         <v>110</v>
@@ -9986,12 +9967,12 @@
         <v>0</v>
       </c>
       <c r="G11" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="B12" s="19">
         <f>B11</f>
@@ -10014,12 +9995,12 @@
         <v>860</v>
       </c>
       <c r="G12" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="B14" s="19">
         <f>'Combined P&amp;L'!B12</f>
@@ -10042,12 +10023,12 @@
         <v>154.46884931506847</v>
       </c>
       <c r="G14" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="B15" s="19">
         <f>B14*0.6</f>
@@ -10070,12 +10051,12 @@
         <v>187.06994383561641</v>
       </c>
       <c r="G15" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="53" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="B17" s="51">
         <f>B12+B15</f>
@@ -10098,12 +10079,12 @@
         <v>1047.0699438356164</v>
       </c>
       <c r="G17" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="44" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="B19" s="19">
         <f>B17-B9</f>
@@ -10126,12 +10107,12 @@
         <v>676.83706712328762</v>
       </c>
       <c r="G19" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="44" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="B21" s="48">
         <f>B17/B7</f>
@@ -10154,12 +10135,12 @@
         <v>0.39593942450142444</v>
       </c>
       <c r="G21" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="B22" t="str">
         <f>IF(B21&gt;=0.13,"✓ PASS","✗ BREACH")</f>
@@ -10182,7 +10163,7 @@
         <v>✓ PASS</v>
       </c>
       <c r="G22" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>
@@ -10224,40 +10205,40 @@
   <sheetData>
     <row r="1" spans="1:6" ht="16">
       <c r="A1" s="42" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="43" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="45" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="B4" s="45" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="C4" s="45" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="D4" s="45" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="E4" s="45" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="F4" s="45" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="B5" s="64">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="C5" s="67">
         <v>150</v>
@@ -10270,12 +10251,12 @@
         <v>6.7000000000000004E-2</v>
       </c>
       <c r="F5" t="s">
-        <v>343</v>
+        <v>585</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="B6" s="64">
         <v>0.1</v>
@@ -10291,12 +10272,12 @@
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="F6" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="B7" s="48">
         <f>equity_pct/100</f>
@@ -10306,92 +10287,92 @@
         <v>0</v>
       </c>
       <c r="F7" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="44" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="B8" s="50">
         <f>B5+B6+B7</f>
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="53" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="B10" s="68">
         <f>(B5*E5+B6*E6)/(B5+B6)*100</f>
-        <v>6.9840909090909093</v>
+        <v>6.9906976744186053</v>
       </c>
       <c r="F10" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="B11" s="23">
         <f>cof_apr</f>
         <v>6.5</v>
       </c>
       <c r="F11" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="B12" s="69">
         <f>(B10-B11)*100</f>
-        <v>48.409090909090935</v>
+        <v>49.069767441860535</v>
       </c>
       <c r="F12" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="B13" t="str">
         <f>IF(B10&lt;B11,"✓ Inputs conservative",IF(B10&lt;=B11+50,"⚠ Within 50 bps","✗ Inputs cof_apr UNDERSTATES cost"))</f>
         <v>⚠ Within 50 bps</v>
       </c>
       <c r="F13" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="45" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="B15" s="45" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C15" s="45" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D15" s="45" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E15" s="45" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="F15" s="45" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B16" s="19">
         <f>'Combined P&amp;L'!B5</f>
@@ -10416,32 +10397,32 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="B17" s="19">
         <f>B16*$B$5</f>
-        <v>39.667808219178085</v>
+        <v>38.650684931506852</v>
       </c>
       <c r="C17" s="19">
         <f>C16*$B$5</f>
-        <v>238.00684931506851</v>
+        <v>231.9041095890411</v>
       </c>
       <c r="D17" s="19">
         <f>D16*$B$5</f>
-        <v>634.68493150684935</v>
+        <v>618.41095890410963</v>
       </c>
       <c r="E17" s="19">
         <f>E16*$B$5</f>
-        <v>1269.3698630136987</v>
+        <v>1236.8219178082193</v>
       </c>
       <c r="F17" s="19">
         <f>F16*$B$5</f>
-        <v>2062.7260273972606</v>
+        <v>2009.8356164383563</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="B18" s="19">
         <f>B16*$B$6</f>
@@ -10466,7 +10447,7 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="B19" s="19">
         <f>B16*$B$7</f>
@@ -10491,12 +10472,12 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="45" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="B22" t="str">
         <f>IF(B17/B16&lt;=0.85,"✓ PASS","✗ BREACH")</f>
@@ -10521,7 +10502,7 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="B23" t="str">
         <f>IF(avg_ticket_k/1000/B16&lt;=0.1,"✓ PASS","✗ BREACH")</f>
@@ -10546,7 +10527,7 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="B24" t="str">
         <f>IF('Capital Plan'!B21&gt;=0.13,"✓ PASS","✗ BREACH")</f>
@@ -10634,50 +10615,50 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="45" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="B1" s="70" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="C1" s="133">
         <f>MATCH(B1,C4:F4,0)</f>
         <v>1</v>
       </c>
       <c r="D1" s="134" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="43" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="80" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="B4" s="81" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="C4" s="80" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="D4" s="81" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="E4" s="82" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="F4" s="83" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="G4" s="80" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="84" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="B5" s="85">
         <f>CHOOSE($C$1,C5,D5,E5,F5)</f>
@@ -10699,12 +10680,12 @@
         <v>2400</v>
       </c>
       <c r="G5" s="84" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="84" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="B6" s="86">
         <f>CHOOSE($C$1,C6,D6,E6,F6)</f>
@@ -10726,12 +10707,12 @@
         <v>1.3</v>
       </c>
       <c r="G6" s="84" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="84" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="B7" s="86">
         <f>CHOOSE($C$1,C7,D7,E7,F7)</f>
@@ -10753,12 +10734,12 @@
         <v>1.5</v>
       </c>
       <c r="G7" s="84" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="84" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="B8" s="86">
         <f>CHOOSE($C$1,C8,D8,E8,F8)</f>
@@ -10780,12 +10761,12 @@
         <v>16</v>
       </c>
       <c r="G8" s="84" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="84" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="B9" s="86">
         <f>CHOOSE($C$1,C9,D9,E9,F9)</f>
@@ -10807,12 +10788,12 @@
         <v>8.5</v>
       </c>
       <c r="G9" s="84" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="84" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="B10" s="86">
         <f>CHOOSE($C$1,C10,D10,E10,F10)</f>
@@ -10834,12 +10815,12 @@
         <v>3.6</v>
       </c>
       <c r="G10" s="84" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="84" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B11" s="86">
         <f>CHOOSE($C$1,C11,D11,E11,F11)</f>
@@ -10861,12 +10842,12 @@
         <v>7.2</v>
       </c>
       <c r="G11" s="84" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="84" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="B12" s="86">
         <f>CHOOSE($C$1,C12,D12,E12,F12)</f>
@@ -10888,12 +10869,12 @@
         <v>18</v>
       </c>
       <c r="G12" s="84" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="84" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="B13" s="86">
         <f>CHOOSE($C$1,C13,D13,E13,F13)</f>
@@ -10915,42 +10896,42 @@
         <v>2.9</v>
       </c>
       <c r="G13" s="84" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="45" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="43" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="80" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="B18" s="81" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="C18" s="80" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="D18" s="81" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="E18" s="82" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="F18" s="83" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="84" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="B19" s="85">
         <f>CHOOSE($C$1,C19,D19,E19,F19)</f>
@@ -10975,7 +10956,7 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="84" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="B20" s="85">
         <f>CHOOSE($C$1,C20,D20,E20,F20)</f>
@@ -11000,7 +10981,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="84" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="B21" s="85">
         <f>CHOOSE($C$1,C21,D21,E21,F21)</f>
@@ -11025,7 +11006,7 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="84" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="B22" s="85">
         <f>CHOOSE($C$1,C22,D22,E22,F22)</f>
@@ -11050,7 +11031,7 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="92" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="B23" s="93">
         <f>CHOOSE($C$1,C23,D23,E23,F23)</f>
@@ -11083,7 +11064,7 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="84" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="B25" s="85">
         <f>CHOOSE($C$1,C25,D25,E25,F25)</f>
@@ -11108,7 +11089,7 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="84" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="B26" s="85">
         <f>CHOOSE($C$1,C26,D26,E26,F26)</f>
@@ -11133,7 +11114,7 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="92" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="B27" s="93">
         <f>CHOOSE($C$1,C27,D27,E27,F27)</f>
@@ -11158,7 +11139,7 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="84" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="B28" s="85">
         <f>CHOOSE($C$1,C28,D28,E28,F28)</f>
@@ -11183,7 +11164,7 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="84" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="B29" s="85">
         <f>CHOOSE($C$1,C29,D29,E29,F29)</f>
@@ -11208,7 +11189,7 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="81" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="B30" s="94">
         <f>CHOOSE($C$1,C30,D30,E30,F30)</f>
@@ -11233,7 +11214,7 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="92" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="B31" s="95">
         <f>CHOOSE($C$1,C31,D31,E31,F31)</f>
@@ -11258,7 +11239,7 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="84" t="s">
-        <v>410</v>
+        <v>582</v>
       </c>
       <c r="B32" s="85">
         <f>CHOOSE($C$1,C32,D32,E32,F32)</f>
@@ -11283,7 +11264,7 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="92" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="B33" s="95">
         <f>CHOOSE($C$1,C33,D33,E33,F33)</f>
@@ -11330,17 +11311,17 @@
   <sheetData>
     <row r="1" spans="1:5" ht="16">
       <c r="A1" s="42" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="43" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="75" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="B4" s="101"/>
       <c r="C4" s="101"/>
@@ -11356,13 +11337,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="102" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="B6" s="98">
         <v>8</v>
       </c>
       <c r="C6" s="71" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="D6" s="71"/>
       <c r="E6" s="78"/>
@@ -11376,14 +11357,14 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="76" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="B8" s="99">
         <f>advance_rate/100*(mix_pay30/100*tenor_pay30+mix_bnpl/100*tenor_bnpl+mix_ext/100*tenor_ext)/365</f>
         <v>0.20342465753424657</v>
       </c>
       <c r="C8" s="100" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="D8" s="71"/>
       <c r="E8" s="78"/>
@@ -11397,24 +11378,24 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="103" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="B10" s="87" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C10" s="87" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D10" s="87" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="E10" s="105" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="76" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="B11" s="73">
         <f>fee_pay30_mo*12</f>
@@ -11435,7 +11416,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="76" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="B12" s="73">
         <f>pd_pay30*lgd_pay30/100</f>
@@ -11463,14 +11444,14 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="89" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="B14" s="73">
         <f>E11-cof_apr-E12-opex_pct*opex_y2_mult</f>
         <v>5.0490909090909089</v>
       </c>
       <c r="C14" s="100" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="D14" s="71"/>
       <c r="E14" s="78"/>
@@ -11484,14 +11465,14 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="76" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="B16" s="99">
         <f>B8*B14/100</f>
         <v>1.0271095890410958E-2</v>
       </c>
       <c r="C16" s="100" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="D16" s="71"/>
       <c r="E16" s="78"/>
@@ -11505,49 +11486,49 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="90" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="B18" s="88">
         <f>B6/B16</f>
         <v>778.88475439789818</v>
       </c>
       <c r="C18" s="100" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="D18" s="71"/>
       <c r="E18" s="78"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="76" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="B19" s="72">
         <f>disb_y2</f>
         <v>1500</v>
       </c>
       <c r="C19" s="71" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="D19" s="71"/>
       <c r="E19" s="78"/>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="76" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="B20" s="72">
         <f>B19-B18</f>
         <v>721.11524560210182</v>
       </c>
       <c r="C20" s="71" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="D20" s="71"/>
       <c r="E20" s="78"/>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="77" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="B21" s="74" t="str">
         <f>IF(B20&gt;0,"✓ PASS — "&amp;TEXT(B20/B18,"0%")&amp;" headroom","✗ BREACH — disb_y2 below break-even")</f>
@@ -11559,7 +11540,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="75" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="B24" s="101"/>
       <c r="C24" s="101"/>
@@ -11575,13 +11556,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="102" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="B26" s="59">
         <v>5</v>
       </c>
       <c r="C26" s="71" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="D26" s="71"/>
       <c r="E26" s="78"/>
@@ -11595,56 +11576,56 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="76" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="B28" s="73">
         <f>E11</f>
         <v>17.214545454545455</v>
       </c>
       <c r="C28" s="71" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D28" s="71"/>
       <c r="E28" s="78"/>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="76" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="B29" s="73">
         <f>opex_pct*opex_y3_mult</f>
         <v>2.4</v>
       </c>
       <c r="C29" s="100" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="D29" s="71"/>
       <c r="E29" s="78"/>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="76" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="B30" s="73">
         <f>B28-cof_apr</f>
         <v>10.714545454545455</v>
       </c>
       <c r="C30" s="100" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="D30" s="71"/>
       <c r="E30" s="78"/>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="76" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="B31" s="73">
         <f>E12</f>
         <v>2.6654545454545455</v>
       </c>
       <c r="C31" s="71" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="D31" s="71"/>
       <c r="E31" s="78"/>
@@ -11658,35 +11639,35 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="76" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="B33" s="73">
         <f>B30-B29-B26</f>
         <v>3.3145454545454545</v>
       </c>
       <c r="C33" s="100" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="D33" s="71"/>
       <c r="E33" s="78"/>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="90" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="B34" s="107">
         <f>IF(B31&gt;0,B33/B31,0)</f>
         <v>1.2435197817189632</v>
       </c>
       <c r="C34" s="71" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="D34" s="71"/>
       <c r="E34" s="78"/>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="76" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="B35" s="71" t="str">
         <f>IF(B34&gt;=1,"PDs can rise "&amp;TEXT(B34-1,"0%")&amp;" before ROA hits "&amp;B26&amp;"%","PDs must FALL "&amp;TEXT(1-B34,"0%")&amp;" to reach ROA "&amp;B26&amp;"%")</f>
@@ -11698,7 +11679,7 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="76" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="B36" s="71" t="str">
         <f>IF(B34&gt;=1.8,"✓ Tolerates Stress — still earns ≥"&amp;B26&amp;"% ROA",IF(B34&gt;=1.5,"⚠ Below Stress; tolerates 1.5× PD","✗ Below 1.5× PD — risk-rate elastic"))</f>
@@ -11710,7 +11691,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="77" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="B37" s="74" t="str">
         <f>IF(B34&gt;=1.3,"✓ Tolerates Downside","✗ Below Downside multiplier")</f>
@@ -11789,42 +11770,42 @@
   <sheetData>
     <row r="1" spans="1:6" ht="16">
       <c r="A1" s="42" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="43" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="45" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="B5" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="C5" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="D5" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="E5" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="F5" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="97" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="B6" s="64">
         <v>0.3</v>
@@ -11839,54 +11820,54 @@
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="134" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="B7" s="134" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="C7" s="134" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="D7" s="134" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="E7" s="134" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="45" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="B10" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="C10" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="D10" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="E10" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="F10" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="44" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="B11" s="19">
         <f>disb_y1</f>
@@ -11905,12 +11886,12 @@
         <v>1.3555479452054795</v>
       </c>
       <c r="F11" s="46" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="44" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="B12" s="19">
         <f>disb_y2</f>
@@ -11929,12 +11910,12 @@
         <v>8.1332876712328783</v>
       </c>
       <c r="F12" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="44" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="B13" s="19">
         <f>disb_y3</f>
@@ -11953,12 +11934,12 @@
         <v>21.688767123287672</v>
       </c>
       <c r="F13" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="44" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="C14" s="49">
         <f>C11+C12+C13</f>
@@ -11967,7 +11948,7 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="44" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="E15" s="49">
         <f>E11+E12+E13</f>
@@ -11976,97 +11957,97 @@
     </row>
     <row r="18" spans="1:26">
       <c r="A18" s="45" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
     </row>
     <row r="19" spans="1:26">
       <c r="A19" s="134" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
     </row>
     <row r="20" spans="1:26">
       <c r="A20" t="s">
+        <v>471</v>
+      </c>
+      <c r="B20" s="45" t="s">
+        <v>472</v>
+      </c>
+      <c r="C20" s="45" t="s">
+        <v>473</v>
+      </c>
+      <c r="D20" s="45" t="s">
+        <v>474</v>
+      </c>
+      <c r="E20" s="45" t="s">
+        <v>475</v>
+      </c>
+      <c r="F20" s="45" t="s">
+        <v>476</v>
+      </c>
+      <c r="G20" s="45" t="s">
+        <v>477</v>
+      </c>
+      <c r="H20" s="45" t="s">
+        <v>444</v>
+      </c>
+      <c r="I20" s="45" t="s">
+        <v>478</v>
+      </c>
+      <c r="J20" s="45" t="s">
+        <v>479</v>
+      </c>
+      <c r="K20" s="45" t="s">
+        <v>480</v>
+      </c>
+      <c r="L20" s="45" t="s">
         <v>481</v>
       </c>
-      <c r="B20" s="45" t="s">
+      <c r="M20" s="45" t="s">
         <v>482</v>
       </c>
-      <c r="C20" s="45" t="s">
+      <c r="N20" s="45" t="s">
+        <v>445</v>
+      </c>
+      <c r="O20" s="45" t="s">
         <v>483</v>
       </c>
-      <c r="D20" s="45" t="s">
+      <c r="P20" s="45" t="s">
         <v>484</v>
       </c>
-      <c r="E20" s="45" t="s">
+      <c r="Q20" s="45" t="s">
         <v>485</v>
       </c>
-      <c r="F20" s="45" t="s">
+      <c r="R20" s="45" t="s">
         <v>486</v>
       </c>
-      <c r="G20" s="45" t="s">
+      <c r="S20" s="45" t="s">
         <v>487</v>
       </c>
-      <c r="H20" s="45" t="s">
-        <v>454</v>
-      </c>
-      <c r="I20" s="45" t="s">
+      <c r="T20" s="45" t="s">
+        <v>446</v>
+      </c>
+      <c r="U20" s="45" t="s">
         <v>488</v>
       </c>
-      <c r="J20" s="45" t="s">
+      <c r="V20" s="45" t="s">
         <v>489</v>
       </c>
-      <c r="K20" s="45" t="s">
+      <c r="W20" s="45" t="s">
         <v>490</v>
       </c>
-      <c r="L20" s="45" t="s">
+      <c r="X20" s="45" t="s">
         <v>491</v>
       </c>
-      <c r="M20" s="45" t="s">
+      <c r="Y20" s="45" t="s">
         <v>492</v>
       </c>
-      <c r="N20" s="45" t="s">
-        <v>455</v>
-      </c>
-      <c r="O20" s="45" t="s">
-        <v>493</v>
-      </c>
-      <c r="P20" s="45" t="s">
-        <v>494</v>
-      </c>
-      <c r="Q20" s="45" t="s">
-        <v>495</v>
-      </c>
-      <c r="R20" s="45" t="s">
-        <v>496</v>
-      </c>
-      <c r="S20" s="45" t="s">
-        <v>497</v>
-      </c>
-      <c r="T20" s="45" t="s">
-        <v>456</v>
-      </c>
-      <c r="U20" s="45" t="s">
-        <v>498</v>
-      </c>
-      <c r="V20" s="45" t="s">
-        <v>499</v>
-      </c>
-      <c r="W20" s="45" t="s">
-        <v>500</v>
-      </c>
-      <c r="X20" s="45" t="s">
-        <v>501</v>
-      </c>
-      <c r="Y20" s="45" t="s">
-        <v>502</v>
-      </c>
       <c r="Z20" s="45" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
     </row>
     <row r="21" spans="1:26">
       <c r="A21" s="44" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="B21" s="48">
         <f>0</f>
@@ -12171,7 +12152,7 @@
     </row>
     <row r="22" spans="1:26">
       <c r="A22" s="44" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="B22" s="66">
         <f>$D$11*B21/100</f>
@@ -12276,7 +12257,7 @@
     </row>
     <row r="23" spans="1:26">
       <c r="A23" s="44" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="B23" s="66">
         <f>$D$12*B21/100</f>
@@ -12381,7 +12362,7 @@
     </row>
     <row r="24" spans="1:26">
       <c r="A24" s="44" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="B24" s="66">
         <f>$D$13*B21/100</f>
@@ -12489,7 +12470,7 @@
     </row>
     <row r="26" spans="1:26">
       <c r="A26" s="44" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="B26" s="19">
         <f>$E$11*B21</f>
@@ -12594,7 +12575,7 @@
     </row>
     <row r="27" spans="1:26">
       <c r="A27" s="44" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="B27" s="19">
         <f>$E$12*B21</f>
@@ -12699,7 +12680,7 @@
     </row>
     <row r="28" spans="1:26">
       <c r="A28" s="44" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="B28" s="19">
         <f>$E$13*B21</f>
@@ -12807,7 +12788,7 @@
     </row>
     <row r="30" spans="1:26">
       <c r="A30" s="53" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="B30" s="108">
         <f>B26+B27+B28</f>
@@ -12931,21 +12912,21 @@
   <sheetData>
     <row r="1" spans="1:4" ht="23">
       <c r="A1" s="1" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="5" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="28">
@@ -12953,219 +12934,219 @@
         <v>10</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="42">
       <c r="A6" s="14" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28">
       <c r="A7" s="14" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28">
       <c r="A8" s="14" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="16">
       <c r="A9" s="14" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="B9" s="62">
         <v>0.02</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="16">
       <c r="A10" s="14" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="B10" s="62">
         <v>0.04</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="16">
       <c r="A11" s="14" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="B11" s="62">
         <v>0.1</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="42">
       <c r="A12" s="14" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="B12" s="61">
         <v>0.35</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="28">
       <c r="A13" s="14" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="B13" s="61">
         <v>0.45</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="16">
       <c r="A14" s="14" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="B14" s="61">
         <v>0.65</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="28">
       <c r="A15" s="14" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="B15" s="61">
         <v>1</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="16">
       <c r="A16" s="14" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="28">
       <c r="A17" s="14" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="16">
       <c r="A18" s="14" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="16">
       <c r="A19" s="14" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="17">
       <c r="A21" s="15" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="28" customHeight="1">
       <c r="A23" s="144" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B23" s="145"/>
       <c r="C23" s="145"/>
@@ -13173,7 +13154,7 @@
     </row>
     <row r="24" spans="1:4" ht="28" customHeight="1">
       <c r="A24" s="144" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="B24" s="145"/>
       <c r="C24" s="145"/>
@@ -13181,7 +13162,7 @@
     </row>
     <row r="25" spans="1:4" ht="28" customHeight="1">
       <c r="A25" s="144" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B25" s="145"/>
       <c r="C25" s="145"/>
@@ -13189,7 +13170,7 @@
     </row>
     <row r="26" spans="1:4" ht="28" customHeight="1">
       <c r="A26" s="144" t="s">
-        <v>556</v>
+        <v>546</v>
       </c>
       <c r="B26" s="145"/>
       <c r="C26" s="145"/>
@@ -13197,7 +13178,7 @@
     </row>
     <row r="27" spans="1:4" ht="28" customHeight="1">
       <c r="A27" s="144" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B27" s="145"/>
       <c r="C27" s="145"/>
@@ -13205,7 +13186,7 @@
     </row>
     <row r="28" spans="1:4" ht="28" customHeight="1">
       <c r="A28" s="144" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B28" s="145"/>
       <c r="C28" s="145"/>
@@ -13213,7 +13194,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>585</v>
+        <v>575</v>
       </c>
     </row>
   </sheetData>
@@ -13245,33 +13226,33 @@
   <sheetData>
     <row r="1" spans="1:11" ht="21">
       <c r="A1" s="109" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="110" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="26" customHeight="1">
       <c r="B4" s="111" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="C4" s="112"/>
       <c r="D4" s="111" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="E4" s="112"/>
       <c r="F4" s="111" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
       <c r="G4" s="112"/>
       <c r="H4" s="111" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
       <c r="I4" s="112"/>
       <c r="J4" s="111" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="K4" s="112"/>
     </row>
@@ -13304,29 +13285,29 @@
     </row>
     <row r="6" spans="1:11" ht="18" customHeight="1">
       <c r="B6" s="118" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="D6" s="118" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="F6" s="118" t="s">
-        <v>574</v>
+        <v>564</v>
       </c>
       <c r="H6" s="118" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="J6" s="118" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
     </row>
     <row r="27" spans="2:9">
       <c r="B27" s="119" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
     </row>
     <row r="28" spans="2:9">
       <c r="B28" s="120" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
     </row>
     <row r="30" spans="2:9">
@@ -13603,7 +13584,7 @@
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="135" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="B40" s="122"/>
       <c r="C40" s="122"/>
@@ -13621,7 +13602,7 @@
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="137" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="B42" s="122"/>
       <c r="C42" s="122"/>
@@ -13631,27 +13612,27 @@
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="136" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="B43" s="137" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C43" s="137" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D43" s="137" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E43" s="137" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="F43" s="137" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="136" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B44" s="136">
         <f>'Volume &amp; Mix'!B5*mix_pay30/100</f>
@@ -13676,7 +13657,7 @@
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="136" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B45" s="136">
         <f>'Volume &amp; Mix'!B5*mix_bnpl/100</f>
@@ -13701,7 +13682,7 @@
     </row>
     <row r="46" spans="1:9">
       <c r="A46" s="136" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B46" s="136">
         <f>'Volume &amp; Mix'!B5*mix_ext/100</f>
@@ -13734,7 +13715,7 @@
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="137" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="B48" s="122"/>
       <c r="C48" s="122"/>
@@ -13744,27 +13725,27 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="136" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="B49" s="137" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C49" s="137" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D49" s="137" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E49" s="137" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="F49" s="137" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="136" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="B50" s="136">
         <f>'Combined P&amp;L'!B16</f>
@@ -13789,7 +13770,7 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="136" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="B51" s="136">
         <f>'Combined P&amp;L'!B17</f>
@@ -13814,7 +13795,7 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="136" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="B52" s="136">
         <f>'Combined P&amp;L'!B18</f>
@@ -13839,7 +13820,7 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="136" t="s">
-        <v>524</v>
+        <v>514</v>
       </c>
       <c r="B53" s="136">
         <f>'Combined P&amp;L'!B19</f>
@@ -13872,7 +13853,7 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="137" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="B55" s="122"/>
       <c r="C55" s="122"/>
@@ -13882,27 +13863,27 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="136" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="B56" s="137" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C56" s="137" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D56" s="137" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E56" s="137" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="F56" s="137" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="136" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="B57" s="136">
         <f>'Combined P&amp;L'!B20</f>
@@ -13927,7 +13908,7 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="136" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="B58" s="136">
         <f>'Combined P&amp;L'!B21</f>
@@ -13989,35 +13970,35 @@
   <sheetData>
     <row r="1" spans="1:6" ht="23">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="138" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="5" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="6" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -14027,75 +14008,75 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B6" s="31">
         <v>250</v>
       </c>
       <c r="C6" s="138" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E6" s="138" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F6" s="139" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B7" s="31">
         <v>1500</v>
       </c>
       <c r="C7" s="138" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E7" s="138" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F7" s="139" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B8" s="31">
         <v>4000</v>
       </c>
       <c r="C8" s="138" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E8" s="138" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F8" s="139" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B9" s="31">
         <v>80</v>
       </c>
       <c r="C9" s="138" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E9" s="138" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F9" s="139" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="6" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B10" s="32"/>
       <c r="C10" s="7"/>
@@ -14105,58 +14086,58 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B11" s="33">
         <v>40</v>
       </c>
       <c r="C11" s="138" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E11" s="138" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F11" s="139" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B12" s="33">
         <v>50</v>
       </c>
       <c r="C12" s="138" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E12" s="138" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F12" s="139" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B13" s="33">
         <v>10</v>
       </c>
       <c r="C13" s="138" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E13" s="138" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F13" s="139" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="6" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B14" s="32"/>
       <c r="C14" s="7"/>
@@ -14166,58 +14147,58 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="3" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B15" s="34">
         <v>30</v>
       </c>
       <c r="C15" s="138" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E15" s="138" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F15" s="139" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B16" s="34">
         <v>105</v>
       </c>
       <c r="C16" s="138" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E16" s="138" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F16" s="139" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B17" s="34">
         <v>180</v>
       </c>
       <c r="C17" s="138" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E17" s="138" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F17" s="139" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B18" s="32"/>
       <c r="C18" s="7"/>
@@ -14227,75 +14208,75 @@
     </row>
     <row r="19" spans="1:6" ht="39">
       <c r="A19" s="3" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B19" s="33">
         <v>1.3</v>
       </c>
       <c r="C19" s="138" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E19" s="138" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F19" s="139" t="s">
-        <v>557</v>
+        <v>547</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="26">
       <c r="A20" s="3" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B20" s="33">
         <v>1.5</v>
       </c>
       <c r="C20" s="138" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E20" s="138" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F20" s="139" t="s">
-        <v>558</v>
+        <v>548</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B21" s="33">
         <v>16</v>
       </c>
       <c r="C21" s="138" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E21" s="138" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F21" s="139" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B22" s="31">
         <v>90</v>
       </c>
       <c r="C22" s="138" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E22" s="138" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F22" s="139" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="6" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B23" s="32"/>
       <c r="C23" s="7"/>
@@ -14311,35 +14292,35 @@
         <v>6.5</v>
       </c>
       <c r="C24" s="138" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E24" s="138" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="F24" s="139" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B25" s="33">
         <v>2.4</v>
       </c>
       <c r="C25" s="138" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E25" s="138" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F25" s="139" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="6" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="7"/>
@@ -14349,72 +14330,72 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="3" t="s">
-        <v>531</v>
+        <v>521</v>
       </c>
       <c r="B27" s="33">
         <f>Risk!B9</f>
         <v>0.7</v>
       </c>
       <c r="C27" s="138" t="s">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="E27" s="130" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="F27" s="139" t="s">
-        <v>533</v>
+        <v>523</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="3" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="B28" s="33">
         <f>Risk!C9</f>
         <v>1.8</v>
       </c>
       <c r="C28" s="138" t="s">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="E28" s="130" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="F28" s="139" t="s">
-        <v>533</v>
+        <v>523</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="3" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="B29" s="33">
         <f>Risk!D9</f>
         <v>6.5</v>
       </c>
       <c r="C29" s="138" t="s">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="E29" s="130" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="F29" s="139" t="s">
-        <v>533</v>
+        <v>523</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="26">
       <c r="A30" s="129" t="s">
-        <v>536</v>
+        <v>526</v>
       </c>
       <c r="B30" s="127"/>
       <c r="C30" s="128"/>
       <c r="E30" s="128"/>
       <c r="F30" s="131" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="6" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B31" s="32"/>
       <c r="C31" s="7"/>
@@ -14424,24 +14405,24 @@
     </row>
     <row r="32" spans="1:6" ht="39">
       <c r="A32" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B32" s="33">
         <v>14</v>
       </c>
       <c r="C32" s="138" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E32" s="138" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="F32" s="139" t="s">
-        <v>559</v>
+        <v>549</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="6" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B33" s="32"/>
       <c r="C33" s="7"/>
@@ -14451,121 +14432,121 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="3" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B34" s="31">
         <v>1.67</v>
       </c>
       <c r="C34" s="138" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E34" s="138" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="F34" s="139" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="3" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B35" s="31">
         <v>1.25</v>
       </c>
       <c r="C35" s="138" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E35" s="138" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="F35" s="139" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="3" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B36" s="8">
         <v>1</v>
       </c>
       <c r="C36" s="138" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E36" s="138" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F36" s="139" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="37" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B37" s="38">
         <v>8000</v>
       </c>
       <c r="C37" s="140" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E37" s="138" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="F37" s="139" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="37" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B38" s="38">
         <v>13000</v>
       </c>
       <c r="C38" s="140" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E38" s="138" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="F38" s="139" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="37" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B39" s="38">
         <v>0.95</v>
       </c>
       <c r="C39" s="140" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E39" s="138" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="F39" s="139" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="37" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B40" s="38">
         <v>0.92</v>
       </c>
       <c r="C40" s="140" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E40" s="138" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="F40" s="139" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -14587,40 +14568,40 @@
   <sheetData>
     <row r="1" spans="1:8" ht="23">
       <c r="A1" s="1" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="138" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="5" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E4" s="39" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="F4" s="39" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B5" s="9">
         <f>disb_y1</f>
@@ -14643,12 +14624,12 @@
         <v>13000</v>
       </c>
       <c r="H5" s="138" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="B6" s="18">
         <f>disb_y1*advance_rate/100</f>
@@ -14671,7 +14652,7 @@
         <v>11700</v>
       </c>
       <c r="H6" s="138" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -14681,12 +14662,12 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="3" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B9" s="18">
         <f>disb_y1*advance_rate/100*tenor_pay30/365*mix_pay30/100</f>
@@ -14709,12 +14690,12 @@
         <v>384.65753424657532</v>
       </c>
       <c r="H9" s="138" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="3" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B10" s="18">
         <f>disb_y1*advance_rate/100*tenor_bnpl/365*mix_bnpl/100</f>
@@ -14737,12 +14718,12 @@
         <v>1682.8767123287671</v>
       </c>
       <c r="H10" s="138" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="3" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B11" s="18">
         <f>disb_y1*advance_rate/100*tenor_ext/365*mix_ext/100</f>
@@ -14765,12 +14746,12 @@
         <v>576.9863013698631</v>
       </c>
       <c r="H11" s="138" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="2" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B13" s="18">
         <f>SUM(B9:B11)</f>
@@ -14793,7 +14774,7 @@
         <v>2644.5205479452056</v>
       </c>
       <c r="H13" s="138" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -14817,43 +14798,43 @@
   <sheetData>
     <row r="1" spans="1:8" ht="16">
       <c r="A1" s="42" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="43" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="45" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B4" s="45" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C4" s="45" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D4" s="45" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E4" s="45" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="F4" s="45" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="G4" s="45" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="H4" s="45" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B5" s="19">
         <f>disb_y1</f>
@@ -14880,12 +14861,12 @@
         <v>1.6853496142826505</v>
       </c>
       <c r="H5" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C6" s="47">
         <f>C5/B5-1</f>
@@ -14904,12 +14885,12 @@
         <v>0.625</v>
       </c>
       <c r="H6" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="B8" s="19">
         <f>B5*advance_rate/100</f>
@@ -14936,12 +14917,12 @@
         <v>1.6853496142826505</v>
       </c>
       <c r="H8" s="46" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="44" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B10" s="49">
         <f>'Volume &amp; Mix'!B13</f>
@@ -14968,17 +14949,17 @@
         <v>1.6853496142826505</v>
       </c>
       <c r="H10" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="45" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B13" s="47">
         <f>'Volume &amp; Mix'!B9/'Volume &amp; Mix'!B13</f>
@@ -15001,12 +14982,12 @@
         <v>0.14545454545454545</v>
       </c>
       <c r="H13" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="B14" s="47">
         <f>'Volume &amp; Mix'!B10/'Volume &amp; Mix'!B13</f>
@@ -15029,12 +15010,12 @@
         <v>0.63636363636363635</v>
       </c>
       <c r="H14" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="B15" s="47">
         <f>'Volume &amp; Mix'!B11/'Volume &amp; Mix'!B13</f>
@@ -15057,7 +15038,7 @@
         <v>0.2181818181818182</v>
       </c>
       <c r="H15" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
     </row>
   </sheetData>
@@ -15080,37 +15061,37 @@
   <sheetData>
     <row r="1" spans="1:6" ht="16">
       <c r="A1" s="42" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="43" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="45" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="B4" s="45" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C4" s="45" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D4" s="45" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="E4" s="45" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="F4" s="45" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="44" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="B5" s="60">
         <v>2</v>
@@ -15126,12 +15107,12 @@
         <v>3</v>
       </c>
       <c r="F5" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="44" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="B6" s="60">
         <v>35</v>
@@ -15143,15 +15124,15 @@
         <v>65</v>
       </c>
       <c r="E6" s="52" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="F6" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="44" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="B7" s="60">
         <v>100</v>
@@ -15163,15 +15144,15 @@
         <v>100</v>
       </c>
       <c r="E7" s="52" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="F7" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="53" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="B9" s="57">
         <f>B5*B6/100*B7/100</f>
@@ -15186,15 +15167,15 @@
         <v>6.5</v>
       </c>
       <c r="E9" s="54" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="F9" s="46" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="55" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B10" s="58">
         <f>E5*B6/100*B7/100</f>
@@ -15209,7 +15190,7 @@
         <v>9.75</v>
       </c>
       <c r="F10" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -15232,40 +15213,40 @@
   <sheetData>
     <row r="1" spans="1:8" ht="23">
       <c r="A1" s="1" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="138" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="5" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="H4" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B5" s="18">
         <f>'Volume &amp; Mix'!B9</f>
@@ -15288,12 +15269,12 @@
         <v>384.65753424657532</v>
       </c>
       <c r="H5" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B6" s="21">
         <f>fee_pay30_mo*12</f>
@@ -15316,12 +15297,12 @@
         <v>15.600000000000001</v>
       </c>
       <c r="H6" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B7" s="18">
         <f>B5*B6/100</f>
@@ -15344,12 +15325,12 @@
         <v>60.006575342465759</v>
       </c>
       <c r="H7" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="3" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B9" s="21">
         <f>cof_apr</f>
@@ -15374,7 +15355,7 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="3" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="B10" s="18">
         <f>B5*B9/100</f>
@@ -15397,12 +15378,12 @@
         <v>25.002739726027393</v>
       </c>
       <c r="H10" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="2" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="B12" s="18">
         <f>B7-B10</f>
@@ -15425,12 +15406,12 @@
         <v>35.003835616438366</v>
       </c>
       <c r="H12" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="3" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="B14" s="21">
         <f>pd_pay30</f>
@@ -15453,12 +15434,12 @@
         <v>2</v>
       </c>
       <c r="H14" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="3" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="B15" s="21">
         <f>lgd_pay30</f>
@@ -15481,12 +15462,12 @@
         <v>35</v>
       </c>
       <c r="H15" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="3" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="B16" s="18">
         <f>B14*B15/100*ead_pay30/100</f>
@@ -15509,12 +15490,12 @@
         <v>0.7</v>
       </c>
       <c r="H16" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="B17" s="9">
         <f>B5*B16/100</f>
@@ -15537,7 +15518,7 @@
         <v>2.692602739726027</v>
       </c>
       <c r="H17" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -15547,7 +15528,7 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="2" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B19" s="9">
         <f>B12-B17</f>
@@ -15570,7 +15551,7 @@
         <v>32.311232876712339</v>
       </c>
       <c r="H19" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -15580,7 +15561,7 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="3" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="B21" s="18">
         <f>opex_pct*opex_y1_mult</f>
@@ -15603,12 +15584,12 @@
         <v>2.2080000000000002</v>
       </c>
       <c r="H21" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="3" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B22" s="21">
         <f>B5*B21/100</f>
@@ -15631,7 +15612,7 @@
         <v>8.4932383561643832</v>
       </c>
       <c r="H22" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -15641,7 +15622,7 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B24" s="10">
         <f>B19-B22</f>
@@ -15664,12 +15645,12 @@
         <v>23.817994520547956</v>
       </c>
       <c r="H24" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B25" s="20">
         <f>B24/B5*100</f>
@@ -15692,7 +15673,7 @@
         <v>6.1920000000000028</v>
       </c>
       <c r="H25" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -15702,7 +15683,7 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="3" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B27" s="9">
         <f>B5*equity_pct/100</f>
@@ -15725,12 +15706,12 @@
         <v>53.852054794520548</v>
       </c>
       <c r="H27" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="3" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B28" s="11">
         <f>IF(B27&gt;0,B24/B27*100,0)</f>
@@ -15753,7 +15734,7 @@
         <v>44.228571428571449</v>
       </c>
       <c r="H28" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -15775,40 +15756,40 @@
   <sheetData>
     <row r="1" spans="1:8" ht="23">
       <c r="A1" s="1" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="138" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="5" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="H4" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B5" s="18">
         <f>'Volume &amp; Mix'!B10</f>
@@ -15831,12 +15812,12 @@
         <v>1682.8767123287671</v>
       </c>
       <c r="H5" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B6" s="21">
         <f>fee_bnpl_mo*12</f>
@@ -15859,12 +15840,12 @@
         <v>18</v>
       </c>
       <c r="H6" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B7" s="18">
         <f>B5*B6/100</f>
@@ -15887,12 +15868,12 @@
         <v>302.91780821917808</v>
       </c>
       <c r="H7" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="3" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B9" s="21">
         <f>cof_apr</f>
@@ -15917,7 +15898,7 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="3" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="B10" s="18">
         <f>B5*B9/100</f>
@@ -15940,12 +15921,12 @@
         <v>109.38698630136987</v>
       </c>
       <c r="H10" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="2" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="B12" s="18">
         <f>B7-B10</f>
@@ -15968,12 +15949,12 @@
         <v>193.53082191780823</v>
       </c>
       <c r="H12" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="3" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="B14" s="21">
         <f>pd_bnpl</f>
@@ -15996,12 +15977,12 @@
         <v>4</v>
       </c>
       <c r="H14" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="3" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="B15" s="21">
         <f>lgd_bnpl</f>
@@ -16024,12 +16005,12 @@
         <v>45</v>
       </c>
       <c r="H15" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="3" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="B16" s="18">
         <f>B14*B15/100*ead_bnpl/100</f>
@@ -16052,12 +16033,12 @@
         <v>1.8</v>
       </c>
       <c r="H16" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="B17" s="9">
         <f>B5*B16/100</f>
@@ -16080,7 +16061,7 @@
         <v>30.291780821917811</v>
       </c>
       <c r="H17" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -16090,7 +16071,7 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="2" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B19" s="9">
         <f>B12-B17</f>
@@ -16113,7 +16094,7 @@
         <v>163.2390410958904</v>
       </c>
       <c r="H19" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -16123,7 +16104,7 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="3" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="B21" s="18">
         <f>opex_pct*opex_y1_mult</f>
@@ -16146,12 +16127,12 @@
         <v>2.2080000000000002</v>
       </c>
       <c r="H21" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="3" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B22" s="21">
         <f>B5*B21/100</f>
@@ -16174,7 +16155,7 @@
         <v>37.157917808219182</v>
       </c>
       <c r="H22" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -16184,7 +16165,7 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B24" s="10">
         <f>B19-B22</f>
@@ -16207,12 +16188,12 @@
         <v>126.08112328767122</v>
       </c>
       <c r="H24" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B25" s="20">
         <f>B24/B5*100</f>
@@ -16235,7 +16216,7 @@
         <v>7.4919999999999991</v>
       </c>
       <c r="H25" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -16245,7 +16226,7 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="3" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B27" s="9">
         <f>B5*equity_pct/100</f>
@@ -16268,12 +16249,12 @@
         <v>235.60273972602738</v>
       </c>
       <c r="H27" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="3" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B28" s="11">
         <f>IF(B27&gt;0,B24/B27*100,0)</f>
@@ -16296,7 +16277,7 @@
         <v>53.514285714285712</v>
       </c>
       <c r="H28" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -16318,40 +16299,40 @@
   <sheetData>
     <row r="1" spans="1:8" ht="23">
       <c r="A1" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="138" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="5" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="H4" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B5" s="18">
         <f>'Volume &amp; Mix'!B11</f>
@@ -16374,12 +16355,12 @@
         <v>576.9863013698631</v>
       </c>
       <c r="H5" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B6" s="21">
         <f>fee_ext_apr</f>
@@ -16402,12 +16383,12 @@
         <v>16</v>
       </c>
       <c r="H6" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B7" s="18">
         <f>B5*B6/100</f>
@@ -16430,12 +16411,12 @@
         <v>92.31780821917809</v>
       </c>
       <c r="H7" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="3" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B9" s="21">
         <f>cof_apr</f>
@@ -16460,7 +16441,7 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="3" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="B10" s="18">
         <f>B5*B9/100</f>
@@ -16483,12 +16464,12 @@
         <v>37.5041095890411</v>
       </c>
       <c r="H10" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="2" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="B12" s="18">
         <f>B7-B10</f>
@@ -16511,12 +16492,12 @@
         <v>54.81369863013699</v>
       </c>
       <c r="H12" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="3" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="B14" s="21">
         <f>pd_ext</f>
@@ -16539,12 +16520,12 @@
         <v>10</v>
       </c>
       <c r="H14" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="3" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="B15" s="21">
         <f>lgd_ext</f>
@@ -16567,12 +16548,12 @@
         <v>65</v>
       </c>
       <c r="H15" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="3" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="B16" s="18">
         <f>B14*B15/100*ead_ext/100</f>
@@ -16595,12 +16576,12 @@
         <v>6.5</v>
       </c>
       <c r="H16" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="B17" s="9">
         <f>B5*B16/100</f>
@@ -16623,7 +16604,7 @@
         <v>37.5041095890411</v>
       </c>
       <c r="H17" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -16633,7 +16614,7 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="2" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B19" s="9">
         <f>B12-B17</f>
@@ -16656,7 +16637,7 @@
         <v>17.30958904109589</v>
       </c>
       <c r="H19" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -16666,7 +16647,7 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="3" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="B21" s="18">
         <f>opex_pct*opex_y1_mult</f>
@@ -16689,12 +16670,12 @@
         <v>2.2080000000000002</v>
       </c>
       <c r="H21" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="3" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B22" s="21">
         <f>B5*B21/100</f>
@@ -16717,7 +16698,7 @@
         <v>12.739857534246578</v>
       </c>
       <c r="H22" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -16727,7 +16708,7 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B24" s="10">
         <f>B19-B22</f>
@@ -16750,12 +16731,12 @@
         <v>4.5697315068493118</v>
       </c>
       <c r="H24" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B25" s="20">
         <f>B24/B5*100</f>
@@ -16778,7 +16759,7 @@
         <v>0.79199999999999926</v>
       </c>
       <c r="H25" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -16788,7 +16769,7 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="3" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B27" s="9">
         <f>B5*equity_pct/100</f>
@@ -16811,12 +16792,12 @@
         <v>80.778082191780825</v>
       </c>
       <c r="H27" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="3" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B28" s="11">
         <f>IF(B27&gt;0,B24/B27*100,0)</f>
@@ -16839,7 +16820,7 @@
         <v>5.657142857142853</v>
       </c>
       <c r="H28" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
